--- a/blueboot_agency_power_agent/output/statistics.xlsx
+++ b/blueboot_agency_power_agent/output/statistics.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26T16:32:22Z</t>
+          <t>2026-05-26T20:40:58Z</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11294</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15749</v>
+        <v>13718</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR, AT, BE, BR, DE, DK, EE, ES, FI, FR, HU, IE, IN, IT, LT, LV, NL, NO, PL, SE, TN, UK, XX</t>
+          <t>*, AR, AT, BE, BR, DE, DK, EE, ES, FI, FR, HU, IE, IN, IT, LT, LV, NL, NO, PL, SE, TN, UK, XX</t>
         </is>
       </c>
     </row>
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7770</v>
+        <v>7071</v>
       </c>
       <c r="C9" t="n">
-        <v>10531</v>
+        <v>9427</v>
       </c>
     </row>
     <row r="10">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1610</v>
+        <v>1364</v>
       </c>
       <c r="C10" t="n">
-        <v>2640</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="11">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1414</v>
+        <v>1200</v>
       </c>
       <c r="C11" t="n">
-        <v>2140</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="12">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="C12" t="n">
-        <v>438</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -656,414 +656,432 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>*</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>4175</v>
       </c>
       <c r="D2" t="n">
-        <v>104</v>
+        <v>5285</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>347</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1027</v>
+        <v>89</v>
       </c>
       <c r="D4" t="n">
-        <v>1697</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>172</v>
+        <v>672</v>
       </c>
       <c r="D5" t="n">
-        <v>173</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1709</v>
+        <v>127</v>
       </c>
       <c r="D6" t="n">
-        <v>2826</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>1036</v>
       </c>
       <c r="D7" t="n">
-        <v>93</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1555</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1566</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>531</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1941</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>1887</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>1023</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>264</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1127</v>
+        <v>96</v>
       </c>
       <c r="D14" t="n">
-        <v>1456</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>760</v>
+        <v>181</v>
       </c>
       <c r="D15" t="n">
-        <v>1015</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>438</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>535</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1806</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2664</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>1366</v>
       </c>
       <c r="D19" t="n">
-        <v>355</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D20" t="n">
-        <v>181</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>663</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1078,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1118,12 +1136,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>*</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1132,21 +1150,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>2814</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>*</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1155,21 +1173,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>593</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>854</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>*</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1178,21 +1196,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>559</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>*</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1201,21 +1219,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1224,21 +1242,21 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>154</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1247,21 +1265,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1270,21 +1288,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1293,21 +1311,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1316,21 +1334,21 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>771</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>1102</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1339,21 +1357,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>436</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1362,21 +1380,21 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1385,21 +1403,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1408,21 +1426,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>521</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>771</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1431,21 +1449,21 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1454,21 +1472,21 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1477,21 +1495,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1500,21 +1518,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>933</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>1662</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1523,21 +1541,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>337</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>537</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1546,21 +1564,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>346</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>558</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1569,21 +1587,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1592,21 +1610,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>585</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>981</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1615,21 +1633,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1638,21 +1656,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1661,21 +1679,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1684,21 +1702,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1707,44 +1725,44 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1753,21 +1771,21 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>990</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>981</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1776,10 +1794,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>289</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1795,14 +1813,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>223</v>
+        <v>350</v>
       </c>
       <c r="E31" t="n">
-        <v>225</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32">
@@ -1818,60 +1836,60 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E32" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E33" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
@@ -1887,14 +1905,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -1910,37 +1928,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1533</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1522</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1956,14 +1974,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>226</v>
+        <v>842</v>
       </c>
       <c r="E38" t="n">
-        <v>221</v>
+        <v>849</v>
       </c>
     </row>
     <row r="39">
@@ -1979,14 +1997,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E39" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
@@ -2002,37 +2020,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E40" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -2048,14 +2066,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2071,37 +2089,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>191</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2117,14 +2135,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46">
@@ -2140,14 +2158,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -2163,37 +2181,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>752</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>1021</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2209,14 +2227,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E49" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50">
@@ -2232,14 +2250,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="E50" t="n">
-        <v>277</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2255,37 +2273,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E51" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>594</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>766</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2301,14 +2319,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>361</v>
       </c>
       <c r="E53" t="n">
-        <v>157</v>
+        <v>457</v>
       </c>
     </row>
     <row r="54">
@@ -2324,14 +2342,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E54" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -2347,37 +2365,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2393,14 +2411,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2416,37 +2434,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2462,14 +2480,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2485,14 +2503,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -2508,7 +2526,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2521,24 +2539,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1435</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>2083</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2554,14 +2572,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>187</v>
+        <v>1111</v>
       </c>
       <c r="E64" t="n">
-        <v>287</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="65">
@@ -2577,14 +2595,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E65" t="n">
-        <v>265</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66">
@@ -2600,37 +2618,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>29</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>D - Low fit</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E67" t="n">
-        <v>277</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -2646,14 +2664,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E68" t="n">
-        <v>55</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69">
@@ -2669,14 +2687,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
@@ -2692,14 +2710,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -2719,10 +2737,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E71" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72">
@@ -2742,10 +2760,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -2765,10 +2783,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -2788,10 +2806,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -2811,10 +2829,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="E75" t="n">
-        <v>183</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76">
@@ -2834,10 +2852,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E76" t="n">
-        <v>224</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77">
@@ -2857,10 +2875,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78">
@@ -2880,10 +2898,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79">
@@ -2903,10 +2921,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
@@ -2922,60 +2940,60 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>D - Low fit</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2991,105 +3009,36 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A - High fit</t>
+          <t>C - Maybe</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>unset</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>C - Maybe</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>18</v>
-      </c>
-      <c r="E85" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>D - Low fit</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>XX</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>XX</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>unset</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" t="n">
         <v>0</v>
       </c>
     </row>
